--- a/docs/Mapping_casi_uso/matrimoni/Sep_Div_999.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Sep_Div_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="103">
   <si>
     <t>Sezione</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>descrizioneMotivoRecupero</t>
+  </si>
+  <si>
+    <t>Identificativo Atto Cartaceo</t>
+  </si>
+  <si>
+    <t>idAttoCartaceo</t>
   </si>
   <si>
     <t>Marito</t>
@@ -373,7 +379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
@@ -663,19 +669,19 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>10</v>
@@ -686,16 +692,16 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>40</v>
@@ -709,16 +715,16 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>42</v>
@@ -732,16 +738,16 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -755,7 +761,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>45</v>
@@ -764,7 +770,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -778,7 +784,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>47</v>
@@ -787,7 +793,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
@@ -801,7 +807,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>49</v>
@@ -810,7 +816,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>50</v>
@@ -824,16 +830,16 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>52</v>
@@ -847,7 +853,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>53</v>
@@ -856,7 +862,7 @@
         <v>25</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>54</v>
@@ -870,7 +876,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>55</v>
@@ -879,7 +885,7 @@
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>56</v>
@@ -893,7 +899,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>57</v>
@@ -902,7 +908,7 @@
         <v>25</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>58</v>
@@ -916,7 +922,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>59</v>
@@ -925,7 +931,7 @@
         <v>25</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>60</v>
@@ -939,16 +945,16 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>62</v>
@@ -962,7 +968,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>63</v>
@@ -971,7 +977,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>64</v>
@@ -985,16 +991,16 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>66</v>
@@ -1008,7 +1014,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>67</v>
@@ -1017,7 +1023,7 @@
         <v>25</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>68</v>
@@ -1031,7 +1037,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>69</v>
@@ -1040,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>70</v>
@@ -1054,7 +1060,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>71</v>
@@ -1063,7 +1069,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>72</v>
@@ -1077,7 +1083,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>73</v>
@@ -1086,7 +1092,7 @@
         <v>25</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>74</v>
@@ -1100,7 +1106,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>75</v>
@@ -1109,7 +1115,7 @@
         <v>25</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>76</v>
@@ -1123,7 +1129,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>77</v>
@@ -1132,7 +1138,7 @@
         <v>25</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>78</v>
@@ -1146,7 +1152,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>79</v>
@@ -1155,7 +1161,7 @@
         <v>25</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>80</v>
@@ -1169,7 +1175,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>81</v>
@@ -1178,7 +1184,7 @@
         <v>25</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>82</v>
@@ -1192,16 +1198,16 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>84</v>
@@ -1215,7 +1221,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>85</v>
@@ -1224,7 +1230,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>86</v>
@@ -1238,16 +1244,16 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>88</v>
@@ -1261,7 +1267,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>89</v>
@@ -1270,7 +1276,7 @@
         <v>25</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>90</v>
@@ -1284,7 +1290,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>91</v>
@@ -1293,7 +1299,7 @@
         <v>25</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>92</v>
@@ -1307,7 +1313,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>93</v>
@@ -1316,7 +1322,7 @@
         <v>25</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>94</v>
@@ -1330,7 +1336,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>95</v>
@@ -1339,7 +1345,7 @@
         <v>25</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>96</v>
@@ -1353,19 +1359,19 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="C43" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>10</v>
@@ -1376,16 +1382,16 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>40</v>
@@ -1399,16 +1405,16 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>42</v>
@@ -1422,16 +1428,16 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>44</v>
@@ -1445,7 +1451,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>45</v>
@@ -1454,7 +1460,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>46</v>
@@ -1468,7 +1474,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>47</v>
@@ -1477,7 +1483,7 @@
         <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>48</v>
@@ -1491,7 +1497,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>49</v>
@@ -1500,7 +1506,7 @@
         <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>50</v>
@@ -1514,16 +1520,16 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>52</v>
@@ -1537,7 +1543,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>53</v>
@@ -1546,7 +1552,7 @@
         <v>25</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>54</v>
@@ -1560,7 +1566,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>55</v>
@@ -1569,7 +1575,7 @@
         <v>25</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>56</v>
@@ -1583,7 +1589,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>57</v>
@@ -1592,7 +1598,7 @@
         <v>25</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>58</v>
@@ -1606,7 +1612,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>59</v>
@@ -1615,7 +1621,7 @@
         <v>25</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>60</v>
@@ -1629,16 +1635,16 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>62</v>
@@ -1652,7 +1658,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>63</v>
@@ -1661,7 +1667,7 @@
         <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>64</v>
@@ -1675,16 +1681,16 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>66</v>
@@ -1698,7 +1704,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>67</v>
@@ -1707,7 +1713,7 @@
         <v>25</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>68</v>
@@ -1721,7 +1727,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>69</v>
@@ -1730,7 +1736,7 @@
         <v>25</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>70</v>
@@ -1744,7 +1750,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>71</v>
@@ -1753,7 +1759,7 @@
         <v>25</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>72</v>
@@ -1767,7 +1773,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>73</v>
@@ -1776,7 +1782,7 @@
         <v>25</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>74</v>
@@ -1790,7 +1796,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>75</v>
@@ -1799,7 +1805,7 @@
         <v>25</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>76</v>
@@ -1813,7 +1819,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>77</v>
@@ -1822,7 +1828,7 @@
         <v>25</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>78</v>
@@ -1836,7 +1842,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>79</v>
@@ -1845,7 +1851,7 @@
         <v>25</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>80</v>
@@ -1859,7 +1865,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>81</v>
@@ -1868,7 +1874,7 @@
         <v>25</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>82</v>
@@ -1882,16 +1888,16 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>84</v>
@@ -1905,7 +1911,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>85</v>
@@ -1914,7 +1920,7 @@
         <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>86</v>
@@ -1928,16 +1934,16 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>88</v>
@@ -1951,7 +1957,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>89</v>
@@ -1960,7 +1966,7 @@
         <v>25</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>90</v>
@@ -1974,7 +1980,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>91</v>
@@ -1983,7 +1989,7 @@
         <v>25</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>92</v>
@@ -1997,7 +2003,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>93</v>
@@ -2006,7 +2012,7 @@
         <v>25</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>94</v>
@@ -2020,7 +2026,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>95</v>
@@ -2029,7 +2035,7 @@
         <v>25</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>96</v>
@@ -2046,21 +2052,44 @@
         <v>99</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D73" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G73" s="2" t="s">
+      <c r="E74" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>16</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/matrimoni/Sep_Div_999.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Sep_Div_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="109">
   <si>
     <t>Sezione</t>
   </si>
@@ -35,6 +35,18 @@
     <t>Condizioni obbligatorieta'</t>
   </si>
   <si>
+    <t>Allegati</t>
+  </si>
+  <si>
+    <t>Allegato generico</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Formula</t>
   </si>
   <si>
@@ -44,9 +56,6 @@
     <t>SI</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Si puo' ignorare la sezione per</t>
   </si>
   <si>
@@ -87,9 +96,6 @@
   </si>
   <si>
     <t>Data decorrenza</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
   <si>
     <t>dataDecorrenza</t>
@@ -391,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
@@ -450,63 +456,63 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
@@ -515,90 +521,90 @@
         <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="F8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>28</v>
@@ -607,21 +613,21 @@
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>30</v>
@@ -630,12 +636,12 @@
         <v>10</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
@@ -644,7 +650,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>32</v>
@@ -653,21 +659,21 @@
         <v>10</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>34</v>
@@ -676,21 +682,21 @@
         <v>10</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>36</v>
@@ -699,44 +705,44 @@
         <v>10</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>42</v>
@@ -745,21 +751,21 @@
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -768,12 +774,12 @@
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>45</v>
@@ -782,7 +788,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -791,21 +797,21 @@
         <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
@@ -814,21 +820,21 @@
         <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>50</v>
@@ -837,12 +843,12 @@
         <v>10</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>51</v>
@@ -851,7 +857,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>52</v>
@@ -860,21 +866,21 @@
         <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>54</v>
@@ -883,21 +889,21 @@
         <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>56</v>
@@ -906,21 +912,21 @@
         <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>58</v>
@@ -929,21 +935,21 @@
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>60</v>
@@ -952,21 +958,21 @@
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>62</v>
@@ -975,21 +981,21 @@
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>64</v>
@@ -998,21 +1004,21 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>66</v>
@@ -1021,12 +1027,12 @@
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>67</v>
@@ -1035,7 +1041,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>68</v>
@@ -1044,21 +1050,21 @@
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>70</v>
@@ -1067,21 +1073,21 @@
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>72</v>
@@ -1090,21 +1096,21 @@
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>74</v>
@@ -1113,21 +1119,21 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>76</v>
@@ -1136,21 +1142,21 @@
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>78</v>
@@ -1159,21 +1165,21 @@
         <v>10</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>80</v>
@@ -1182,21 +1188,21 @@
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>82</v>
@@ -1205,21 +1211,21 @@
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>84</v>
@@ -1228,21 +1234,21 @@
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>86</v>
@@ -1251,21 +1257,21 @@
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>88</v>
@@ -1274,12 +1280,12 @@
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>89</v>
@@ -1288,7 +1294,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>90</v>
@@ -1297,21 +1303,21 @@
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>92</v>
@@ -1320,21 +1326,21 @@
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>94</v>
@@ -1343,21 +1349,21 @@
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>96</v>
@@ -1366,21 +1372,21 @@
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>98</v>
@@ -1389,21 +1395,21 @@
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>100</v>
@@ -1412,21 +1418,21 @@
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>102</v>
@@ -1435,44 +1441,44 @@
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="C46" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="F46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>42</v>
@@ -1481,21 +1487,21 @@
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>44</v>
@@ -1504,12 +1510,12 @@
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>45</v>
@@ -1518,7 +1524,7 @@
         <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>46</v>
@@ -1527,21 +1533,21 @@
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>48</v>
@@ -1550,21 +1556,21 @@
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>50</v>
@@ -1573,12 +1579,12 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>51</v>
@@ -1587,7 +1593,7 @@
         <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>52</v>
@@ -1596,21 +1602,21 @@
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>54</v>
@@ -1619,21 +1625,21 @@
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>56</v>
@@ -1642,21 +1648,21 @@
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>58</v>
@@ -1665,21 +1671,21 @@
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>60</v>
@@ -1688,21 +1694,21 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>62</v>
@@ -1711,21 +1717,21 @@
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>64</v>
@@ -1734,21 +1740,21 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>66</v>
@@ -1757,12 +1763,12 @@
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>67</v>
@@ -1771,7 +1777,7 @@
         <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>68</v>
@@ -1780,21 +1786,21 @@
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>70</v>
@@ -1803,21 +1809,21 @@
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>72</v>
@@ -1826,21 +1832,21 @@
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>74</v>
@@ -1849,21 +1855,21 @@
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>76</v>
@@ -1872,21 +1878,21 @@
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>78</v>
@@ -1895,21 +1901,21 @@
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>80</v>
@@ -1918,21 +1924,21 @@
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>82</v>
@@ -1941,21 +1947,21 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>84</v>
@@ -1964,21 +1970,21 @@
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>86</v>
@@ -1987,21 +1993,21 @@
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>88</v>
@@ -2010,12 +2016,12 @@
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>89</v>
@@ -2024,7 +2030,7 @@
         <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>90</v>
@@ -2033,21 +2039,21 @@
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>92</v>
@@ -2056,21 +2062,21 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>94</v>
@@ -2079,21 +2085,21 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>96</v>
@@ -2102,21 +2108,21 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>98</v>
@@ -2125,21 +2131,21 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>100</v>
@@ -2148,21 +2154,21 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>102</v>
@@ -2171,7 +2177,7 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78">
@@ -2179,22 +2185,45 @@
         <v>105</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>14</v>
+        <v>106</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
